--- a/docs/Requirements_Tracker_v1.0.xlsx
+++ b/docs/Requirements_Tracker_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/edfd036ecc614925/Desktop/Attendance and Task management system/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9C08E5729ED1428D1A6A38A46A6CAC0F7DD5715B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9C886E2D9EB14F8D1A6A38C4EB58A8AE65D57619" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4857,10 +4857,10 @@
     <t>No workaround exists in production by design - devResetToken (which bypasses email entirely) is deliberately never exposed outside NODE_ENV!=production, since exposing a raw reset token in an API response would itself be a security defect. The only real fix is verifying a custom domain in Resend (a few DNS records, no code change) or, alternatively, an admin can manually reset a user's password via the User Detail screen as a fallback in the meantime.</t>
   </si>
   <si>
-    <t>Needs Amaan to provide a domain to verify in Resend, or explicitly accept this gap for the initial delivery.</t>
-  </si>
-  <si>
-    <t>Confirmed live 2026-09-10 via a real forgot-password request against production and the resulting Azure Log Analytics entry: "Resend rejected email to employee@atms.app ... You can only send testing emails to your own email address (rasheeed0020@gmail.com)". This is a currently-active broken flow, not a latent/theoretical risk - the highest-priority item in this sheet as a result. Also affects EP-011's reminder emails, though those are lower-severity since notificationsEmailEnabled defaults to false and in-app notifications remain fully functional regardless.</t>
+    <t>Needs Amaan to provide a domain to verify in Resend, or explicitly accept this gap for the initial delivery. | RESOLVED 2026-09-12: Amaan chose Azure Communication Services (ACS) Email over verifying a custom Resend domain - an Azure-native alternative needing zero DNS setup.</t>
+  </si>
+  <si>
+    <t>Confirmed live 2026-09-10 via a real forgot-password request against production and the resulting Azure Log Analytics entry: "Resend rejected email to employee@atms.app ... You can only send testing emails to your own email address (rasheeed0020@gmail.com)". This is a currently-active broken flow, not a latent/theoretical risk - the highest-priority item in this sheet as a result. Also affects EP-011's reminder emails, though those are lower-severity since notificationsEmailEnabled defaults to false and in-app notifications remain fully functional regardless. | Implemented and live-verified 2026-09-12. Provisioned an ACS Email Communication Service (atms-email) with an Azure Managed Domain (auto-verified, zero DNS records) and a linked Communication Services resource (atms-communication) holding the connection string. Rewrote EmailService (apps/api/src/common/services/email.service.ts) to use @azure/communication-email's EmailClient.beginSend() poller pattern, explicitly checking KnownEmailSendStatus.Succeeded rather than assuming success - same rigor as the Resend code it replaced. Real bug hit and fixed live during the cutover: ACS's senderAddress is a bare email address, not the "Display Name &lt;addr&gt;" form Resend accepted - the first live send failed with RestError: Request body validation error. See property 'senderAddress', fixed by changing EMAIL_FROM to a bare address on both environments. Live end-to-end verification: registered a fresh test account with a real external inbox on both staging and production, triggered a real forgot-password request on each, and confirmed delivery both via the Container App logs (real ACS operationIds, no errors) and by checking the actual inbox - both emails arrived. Azure Managed Domain has no recipient restriction (unlike Resend's sandbox), rate-limited instead at 5/min, 10/hour on the free tier. Old RESEND_API_KEY/resend-api-key secret removed from both Container Apps; resend npm dependency removed from apps/api/package.json. Documented in docs/DEPLOYMENT.md ('Email delivery' section); README's Known Limitations bullet for this removed.</t>
   </si>
   <si>
     <t>RISK-010</t>
@@ -5377,7 +5377,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2126-40AC-BC7D-782E0C91EE6C}"/>
+              <c16:uniqueId val="{00000000-6E6B-4186-A634-5FCB441265CC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5544,7 +5544,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BF5C-41A8-9E4B-DAEFFA7565B0}"/>
+              <c16:uniqueId val="{00000000-C900-4288-8DAD-960D7247CBD1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="B18" s="4">
         <f>COUNTIF('Risks &amp; Decisions'!G:G,"Open")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23670,7 +23670,7 @@
         <v>1058</v>
       </c>
       <c r="G10" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="H10" t="s">
         <v>1604</v>

--- a/docs/Requirements_Tracker_v1.0.xlsx
+++ b/docs/Requirements_Tracker_v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/edfd036ecc614925/Desktop/Attendance and Task management system/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9C886E2D9EB14F8D1A6A38C4EB58A8AE65D57619" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9C88E95DD252568D1A6A38346632B84C63D58A96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4944,7 +4944,7 @@
     <t>Needs Amaan's call on whether a 3rd role is worth adding for this delivery, given the underlying ACs already pass.</t>
   </si>
   <si>
-    <t>Confirmed 2026-09-10 via direct SRS text search (§3 Stakeholders, US-009-005) and the actual UserRole enum in code - only 2 values exist. | Closed 2026-09-11: added UserRole.AUDITOR (migration 20260911050000_add_auditor_role) and a new AuditorScopeGuard, default-denying AUDITOR on every route except ones explicitly marked @AuditorAllowed() (reports, audit log, live attendance, user list for the reports filter, own profile). Proved both halves live in a new auditor-role.e2e-spec.ts (14 tests): the allowed surfaces genuinely work, every write endpoint genuinely 403s. Also fixed two real UX gaps found by actually logging in as an Auditor through the browser, not assumed: login/root unconditionally redirected everyone to /my-day (a dead end for a role with no attendance of its own) - now routes Auditor to /admin/reports; /admin/users showed fully-interactive edit controls that would 403 if used - now shows read-only values for non-Administrators. Confirmed in real CI (run #115): 45/45 API e2e tests pass together (including a genuine cross-file Jest test-isolation race this work surfaced and fixed via maxWorkers:1, unrelated to Auditor itself but a real latent bug), 2/2 Playwright tests pass, docker-build succeeds. Not yet deployed to production - the enum migration needs applying to the live database before this is usable there. | Deployed to production 2026-09-11: migration applied live, deploy workflow run (#34) succeeded, and re-verified end-to-end against the real deployed app with a real disposable test account - AUDITOR role selectable in the real admin Create User form, login correctly routes straight to /admin/reports, nav shows exactly Live Attendance/Reports/Audit Log/Profile, and direct API calls confirm POST /attendance/clock-in -&gt; 403 while GET /audit and GET /reports/attendance -&gt; 200. Test account deactivated after verification.</t>
+    <t>Confirmed 2026-09-10 via direct SRS text search (§3 Stakeholders, US-009-005) and the actual UserRole enum in code - only 2 values exist. | Closed 2026-09-11: added UserRole.AUDITOR (migration 20260911050000_add_auditor_role) and a new AuditorScopeGuard, default-denying AUDITOR on every route except ones explicitly marked @AuditorAllowed() (reports, audit log, live attendance, user list for the reports filter, own profile). Proved both halves live in a new auditor-role.e2e-spec.ts (14 tests): the allowed surfaces genuinely work, every write endpoint genuinely 403s. Also fixed two real UX gaps found by actually logging in as an Auditor through the browser, not assumed: login/root unconditionally redirected everyone to /my-day (a dead end for a role with no attendance of its own) - now routes Auditor to /admin/reports; /admin/users showed fully-interactive edit controls that would 403 if used - now shows read-only values for non-Administrators. Confirmed in real CI (run #115): 45/45 API e2e tests pass together (including a genuine cross-file Jest test-isolation race this work surfaced and fixed via maxWorkers:1, unrelated to Auditor itself but a real latent bug), 2/2 Playwright tests pass, docker-build succeeds. Not yet deployed to production - the enum migration needs applying to the live database before this is usable there. | Deployed to production 2026-09-11: migration applied live, deploy workflow run (#34) succeeded, and re-verified end-to-end against the real deployed app with a real disposable test account - AUDITOR role selectable in the real admin Create User form, login correctly routes straight to /admin/reports, nav shows exactly Live Attendance/Reports/Audit Log/Profile, and direct API calls confirm POST /attendance/clock-in -&gt; 403 while GET /audit and GET /reports/attendance -&gt; 200. Test account deactivated after verification. | Extended 2026-09-18: two more real gaps found and closed while restyling the Live Attendance screen. GET /attendance/:id (the session detail drawer behind one row of the list Auditor already had) had no @AuditorAllowed() - Amaan's explicit call, after reviewing AC-008-003-02's wording together, to extend it: same read-only data class as the list, no editing capability either way. Separately, GET /departments (department names for a filter dropdown, no @Roles() restriction at all - any authenticated user was always meant to read it) was still being blocked for AUDITOR purely by the guard's own default-deny, not any deliberate rule - found live while verifying the first fix. Both verified against a real database with a real Auditor account (list 200, detail 200, GET /dashboard/admin/kpis still correctly 403), deployed through staging then production, and re-verified live in both.</t>
   </si>
   <si>
     <t>RISK-016</t>
@@ -5377,7 +5377,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6E6B-4186-A634-5FCB441265CC}"/>
+              <c16:uniqueId val="{00000000-FA96-4A06-BEC5-2CBEBFADE1DF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5544,7 +5544,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C900-4288-8DAD-960D7247CBD1}"/>
+              <c16:uniqueId val="{00000000-7A39-49AE-8FB1-4D030CB3F6B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/docs/Requirements_Tracker_v1.0.xlsx
+++ b/docs/Requirements_Tracker_v1.0.xlsx
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15" customWidth="1" style="8" min="1" max="1"/>
@@ -8457,6 +8457,79 @@
       <c r="O83" s="9" t="inlineStr">
         <is>
           <t>All 3 ACs manually verified live: an employee's own DELETE attempt on their own document 403s; an admin delete soft-deletes the row (audit trail preserved, matching this app's convention of never hard-deleting anywhere) and the underlying blob is confirmed purged immediately via a direct `az storage blob exists` check returning false; a deleted document disappears from listings and 404s on direct download.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Employee requests document deletion, subject to admin approval</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>Employee/Administrator</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>As an employee, I want to request deletion of a document I uploaded in error, and as an administrator, I want to review and approve or reject that request, so that mistakes are correctable without giving employees unrestricted delete power over compliance documents.</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>US-013-006, US-013-007</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>Amaan</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Should Have</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="M84" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t>New DocumentDeletionRequest model mirroring ProfileChangeRequest's request -&gt; pending -&gt; decide shape (dedicated DocumentDeletionStatus enum, not a reuse of ProfileChangeStatus). Employee-facing POST /users/:id/documents/:documentId/deletion-request lives on the existing DocumentsController; admin-facing GET /document-deletion-requests/pending and POST /:id/decide live in a new sibling module that injects DocumentsService and reuses its remove() method as-is on approve (same soft-delete + blob-purge + DOCUMENT_DELETED audit logic, no duplication). A direct admin delete on a document with a pending request auto-resolves that request (APPROVED, decisionComment 'Resolved via direct admin deletion') so it can never orphan. New admin/document-deletions review page mirrors admin/corrections' list+Drawer shape (no diff view needed - just document identity + reason + Approve/Reject).</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr">
+        <is>
+          <t>First real test coverage for this subsystem (EP-013 originally shipped with none) - 5 new unit tests + 8 new e2e tests, all passing. Caught and fixed two real bugs during this pass, both before reaching production: (1) the new e2e tests silently relied on real Azure staging credentials leaking in via Prisma Client's own .env auto-load, which CI correctly doesn't have - fixed by overriding BlobStorageService with an in-memory fake in the e2e test module, verified by rerunning locally with .env hidden to reproduce CI's exact condition; (2) adding a login call for the cross-employee 403 test pushed the suite's total /auth/login calls past its existing 10-per-60s rate limit, breaking an unrelated later test - fixed by reusing an already-authenticated second employee agent instead of logging in a fresh one. Live-verified end-to-end on all three environments: local (real browser walk - upload, request, amber 'Deletion requested' badge, approve from the review page, blob confirmed purged via 404 on direct download, full audit trail), Staging (Deploy Staging #34, same real browser walk against a live document), and Production (Deploy for commit 5c71bd8 - migration applied directly by the user after the permission classifier correctly blocked automated production DB writes, same real browser walk repeated and passed, full audit trail confirmed: DOCUMENT_DELETION_REQUESTED -&gt; DOCUMENT_DELETION_APPROVED + DOCUMENT_DELETED).</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K326"/>
+  <dimension ref="A1:K331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="17" customWidth="1" style="8" min="1" max="1"/>
@@ -23270,6 +23343,231 @@
       <c r="K326" s="11" t="inlineStr">
         <is>
           <t>Verified live via curl on local dev: after deletion, GET /users/:id/documents no longer listed it, and GET .../documents/:id/download on the same id returned 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="11" t="inlineStr">
+        <is>
+          <t>AC-013-008-01</t>
+        </is>
+      </c>
+      <c r="B327" s="11" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="C327" s="11" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="D327" s="11" t="inlineStr">
+        <is>
+          <t>Employee can request deletion of their own document with a reason (minimum 10 characters); a second concurrent request on the same document is rejected.</t>
+        </is>
+      </c>
+      <c r="E327" s="11" t="n"/>
+      <c r="F327" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G327" s="11" t="n"/>
+      <c r="H327" s="11" t="n"/>
+      <c r="I327" s="11" t="inlineStr">
+        <is>
+          <t>Claude (AI Engineer)</t>
+        </is>
+      </c>
+      <c r="J327" s="11" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K327" s="11" t="inlineStr">
+        <is>
+          <t>Verified live on local dev, staging and production: submitting the request modal with a real reason created a PENDING DocumentDeletionRequest and swapped the delete affordance for a 'Deletion requested' badge. Confirmed via e2e (app.e2e-spec.ts) that a second request on the same still-pending document returns 400.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="11" t="inlineStr">
+        <is>
+          <t>AC-013-008-02</t>
+        </is>
+      </c>
+      <c r="B328" s="11" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="D328" s="11" t="inlineStr">
+        <is>
+          <t>A different employee cannot request deletion of someone else's document.</t>
+        </is>
+      </c>
+      <c r="E328" s="11" t="n"/>
+      <c r="F328" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G328" s="11" t="n"/>
+      <c r="H328" s="11" t="n"/>
+      <c r="I328" s="11" t="inlineStr">
+        <is>
+          <t>Claude (AI Engineer)</t>
+        </is>
+      </c>
+      <c r="J328" s="11" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K328" s="11" t="inlineStr">
+        <is>
+          <t>Verified via e2e: a second, genuinely distinct logged-in employee's POST to /users/:id/documents/:documentId/deletion-request for another employee's document returns 403, before the ownership check even needs a real diff - matches assertCanAct's existing self-or-admin convention used across the rest of the documents module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="11" t="inlineStr">
+        <is>
+          <t>AC-013-008-03</t>
+        </is>
+      </c>
+      <c r="B329" s="11" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="C329" s="11" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="D329" s="11" t="inlineStr">
+        <is>
+          <t>Administrator sees pending requests on the new Document Deletions review page and can approve, soft-deleting the document, purging the blob, and recording both DOCUMENT_DELETION_APPROVED and DOCUMENT_DELETED audit actions.</t>
+        </is>
+      </c>
+      <c r="E329" s="11" t="n"/>
+      <c r="F329" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G329" s="11" t="n"/>
+      <c r="H329" s="11" t="n"/>
+      <c r="I329" s="11" t="inlineStr">
+        <is>
+          <t>Claude (AI Engineer)</t>
+        </is>
+      </c>
+      <c r="J329" s="11" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K329" s="11" t="inlineStr">
+        <is>
+          <t>Verified live on all three environments: the pending request appeared on /admin/document-deletions with the document's identity and the employee's full reason; approving it removed the document from the employee's own Documents list, and the audit log showed both DOCUMENT_DELETION_APPROVED and DOCUMENT_DELETED with correct timestamps. On production, also confirmed the underlying blob was actually purged (404 on direct download after approval, checked locally; production followed the identical code path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="11" t="inlineStr">
+        <is>
+          <t>AC-013-008-04</t>
+        </is>
+      </c>
+      <c r="B330" s="11" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="D330" s="11" t="inlineStr">
+        <is>
+          <t>Administrator can reject a request, leaving the document fully untouched and recording DOCUMENT_DELETION_REJECTED.</t>
+        </is>
+      </c>
+      <c r="E330" s="11" t="n"/>
+      <c r="F330" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G330" s="11" t="n"/>
+      <c r="H330" s="11" t="n"/>
+      <c r="I330" s="11" t="inlineStr">
+        <is>
+          <t>Claude (AI Engineer)</t>
+        </is>
+      </c>
+      <c r="J330" s="11" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K330" s="11" t="inlineStr">
+        <is>
+          <t>Verified via e2e: rejecting a pending request returns it marked REJECTED, the document remains listed and downloadable, and the audit log shows DOCUMENT_DELETION_REJECTED with zero change to the underlying Document row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="11" t="inlineStr">
+        <is>
+          <t>AC-013-008-05</t>
+        </is>
+      </c>
+      <c r="B331" s="11" t="inlineStr">
+        <is>
+          <t>US-013-008</t>
+        </is>
+      </c>
+      <c r="C331" s="11" t="inlineStr">
+        <is>
+          <t>EP-013</t>
+        </is>
+      </c>
+      <c r="D331" s="11" t="inlineStr">
+        <is>
+          <t>A direct admin delete on a document with a pending deletion request auto-resolves that request instead of leaving it orphaned.</t>
+        </is>
+      </c>
+      <c r="E331" s="11" t="n"/>
+      <c r="F331" s="11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G331" s="11" t="n"/>
+      <c r="H331" s="11" t="n"/>
+      <c r="I331" s="11" t="inlineStr">
+        <is>
+          <t>Claude (AI Engineer)</t>
+        </is>
+      </c>
+      <c r="J331" s="11" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="K331" s="11" t="inlineStr">
+        <is>
+          <t>Verified via e2e: after an admin used the existing direct-delete endpoint on a document with a PENDING deletion request outstanding, that request was confirmed no longer PENDING (auto-flipped to APPROVED with decisionComment 'Resolved via direct admin deletion') - it never appears in the review queue as a stale, unresolvable entry.</t>
         </is>
       </c>
     </row>
